--- a/output/HS_Code_Summary_Ponature_IV26-00126.xlsx
+++ b/output/HS_Code_Summary_Ponature_IV26-00126.xlsx
@@ -840,23 +840,23 @@
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="11">
         <f>SUM(E2:E5)</f>
-        <v/>
+        <v>7399</v>
       </c>
       <c r="F6" s="12">
         <f>SUM(F2:F5)</f>
-        <v/>
+        <v>6499.335</v>
       </c>
       <c r="G6" s="12">
         <f>SUM(G2:G5)</f>
-        <v/>
+        <v>7474.535</v>
       </c>
       <c r="H6" s="11">
         <f>SUM(H2:H5)</f>
-        <v/>
+        <v>764</v>
       </c>
       <c r="I6" s="13">
         <f>SUM(I2:I5)</f>
-        <v/>
+        <v>164228.14</v>
       </c>
       <c r="J6" s="10" t="n"/>
       <c r="K6" s="8" t="n"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="C19" s="18">
         <f>E6</f>
-        <v/>
+        <v>7399</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="C20" s="19">
         <f>I6</f>
-        <v/>
+        <v>164228.14</v>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C21" s="20">
         <f>G6</f>
-        <v/>
+        <v>7474.535</v>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C22" s="18">
         <f>H6</f>
-        <v/>
+        <v>764</v>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
